--- a/VerveStacks_TUR_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_TUR_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_TUR_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51FCA156-A9CC-4605-AFF5-D6D56B57C98E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D83D01-3DFA-4972-A36B-2753678CA9D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="11422" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="12772" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="emissions" sheetId="5" r:id="rId1"/>
@@ -4325,7 +4325,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D3DFE4-E469-4A8F-816F-7420400C7833}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA9A36C0-8549-47C6-998D-89342E51CEBA}">
   <dimension ref="B2:AG902"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25706,7 +25706,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{668D9B47-A16A-486B-B38B-3285D82AD262}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F3641D7-B308-47DF-A6D4-137819AB0984}">
   <dimension ref="B9:L32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -39070,7 +39070,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC455410-0832-4526-9FEE-3FB6700FB865}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF48E2A6-E2B6-40C7-A169-3082036F7C8E}">
   <dimension ref="A1:I80"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
